--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.40316896794357</v>
+        <v>10.79051495729083</v>
       </c>
       <c r="D2" t="n">
-        <v>66.37059514436237</v>
+        <v>10.78522171095888</v>
       </c>
       <c r="E2" t="n">
-        <v>1.723379707826774</v>
+        <v>0.2800492025218507</v>
       </c>
       <c r="F2" t="n">
-        <v>1.801727617807908</v>
+        <v>0.2927807378937856</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.36322195552235</v>
+        <v>11.27152356777238</v>
       </c>
       <c r="D3" t="n">
-        <v>69.51616865911492</v>
+        <v>11.29637740710618</v>
       </c>
       <c r="E3" t="n">
-        <v>1.723379707826774</v>
+        <v>0.2800492025218507</v>
       </c>
       <c r="F3" t="n">
-        <v>1.801727617807908</v>
+        <v>0.2927807378937856</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.4896746983883</v>
+        <v>11.4545721384881</v>
       </c>
       <c r="D4" t="n">
-        <v>70.62424487603225</v>
+        <v>11.47643979235524</v>
       </c>
       <c r="E4" t="n">
-        <v>1.723379707826774</v>
+        <v>0.2800492025218507</v>
       </c>
       <c r="F4" t="n">
-        <v>1.801727617807908</v>
+        <v>0.2927807378937856</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
